--- a/StructureDefinition-Provbehallare-Resurs.xlsx
+++ b/StructureDefinition-Provbehallare-Resurs.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T08:41:45+00:00</t>
+    <t>2026-09-18T09:59:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/StructureDefinition-Provbehallare-Resurs.xlsx
+++ b/StructureDefinition-Provbehallare-Resurs.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="88">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="90">
   <si>
     <t>Property</t>
   </si>
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-09-18T09:59:15+00:00</t>
+    <t>2026-09-18T10:29:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -81,7 +81,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Supporting logical model generated from gloo4.xmi (source class: Provbehållare : Resurs).</t>
+    <t>Klassen Provbehållare håller information om den eller de provbehållare som provet förvaras i.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -260,6 +260,9 @@
     <t>Source attribute: id; renamed from reserved FSH name 'id'</t>
   </si>
   <si>
+    <t>Angivelse av identitetsbeteckning för en provbehållare.</t>
+  </si>
+  <si>
     <t>Provbehallare-Resurs.typ</t>
   </si>
   <si>
@@ -271,6 +274,10 @@
   </si>
   <si>
     <t>Source attribute: typ</t>
+  </si>
+  <si>
+    <t>Kod för typ av provbehållare.
+Om kod inte kan anges från nationellt urval kan originalText användas för textalternativ.</t>
   </si>
   <si>
     <t>Provbehallare-Resurs.forvarasI</t>
@@ -866,7 +873,7 @@
         <v>80</v>
       </c>
       <c r="M3" t="s" s="2">
-        <v>80</v>
+        <v>81</v>
       </c>
       <c r="N3" s="2"/>
       <c r="O3" s="2"/>
@@ -934,10 +941,10 @@
     </row>
     <row r="4">
       <c r="A4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="C4" s="2"/>
       <c r="D4" t="s" s="2">
@@ -945,10 +952,10 @@
       </c>
       <c r="E4" s="2"/>
       <c r="F4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="G4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="H4" t="s" s="2">
         <v>20</v>
@@ -960,13 +967,13 @@
         <v>20</v>
       </c>
       <c r="K4" t="s" s="2">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="L4" t="s" s="2">
-        <v>84</v>
+        <v>85</v>
       </c>
       <c r="M4" t="s" s="2">
-        <v>84</v>
+        <v>86</v>
       </c>
       <c r="N4" s="2"/>
       <c r="O4" s="2"/>
@@ -1017,13 +1024,13 @@
         <v>20</v>
       </c>
       <c r="AF4" t="s" s="2">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="AG4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AH4" t="s" s="2">
-        <v>82</v>
+        <v>83</v>
       </c>
       <c r="AI4" t="s" s="2">
         <v>20</v>
@@ -1034,10 +1041,10 @@
     </row>
     <row r="5">
       <c r="A5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="B5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="C5" s="2"/>
       <c r="D5" t="s" s="2">
@@ -1060,13 +1067,13 @@
         <v>20</v>
       </c>
       <c r="K5" t="s" s="2">
-        <v>86</v>
+        <v>88</v>
       </c>
       <c r="L5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="M5" t="s" s="2">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="N5" s="2"/>
       <c r="O5" s="2"/>
@@ -1117,7 +1124,7 @@
         <v>20</v>
       </c>
       <c r="AF5" t="s" s="2">
-        <v>85</v>
+        <v>87</v>
       </c>
       <c r="AG5" t="s" s="2">
         <v>73</v>
